--- a/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0005_ses-01_GMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion PDFs/Example data NIfTI PDF shape covariation/reference_data/pdf_gmprob/sub-0005_ses-01_GMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13641,7 +13640,7 @@
         <v>0</v>
       </c>
       <c r="W38" s="0">
-        <v>0.20512820512820496</v>
+        <v>0.20512820512820495</v>
       </c>
       <c r="X38" s="0">
         <v>0</v>
@@ -13899,7 +13898,7 @@
         <v>0.1092896174863387</v>
       </c>
       <c r="DE38" s="0">
-        <v>0.096665055582406873</v>
+        <v>0.096665055582406872</v>
       </c>
       <c r="DF38" s="0">
         <v>0</v>
@@ -14407,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="0">
-        <v>0.62402496099843941</v>
+        <v>0.6240249609984394</v>
       </c>
       <c r="AL40" s="0">
         <v>0.019346101760495241</v>
@@ -14470,7 +14469,7 @@
         <v>1.2658227848101253</v>
       </c>
       <c r="BF40" s="0">
-        <v>0.29154518950437292</v>
+        <v>0.29154518950437291</v>
       </c>
       <c r="BG40" s="0">
         <v>0</v>
@@ -14497,7 +14496,7 @@
         <v>0</v>
       </c>
       <c r="BO40" s="0">
-        <v>0.30395136778115473</v>
+        <v>0.30395136778115472</v>
       </c>
       <c r="BP40" s="0">
         <v>0.61728395061728336</v>
@@ -14799,7 +14798,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="0">
-        <v>1.0571216617210733</v>
+        <v>1.0571216617210732</v>
       </c>
       <c r="AV41" s="0">
         <v>3.5323049407556613</v>
@@ -14847,7 +14846,7 @@
         <v>0</v>
       </c>
       <c r="BK41" s="0">
-        <v>3.7502575726355008</v>
+        <v>3.7502575726355007</v>
       </c>
       <c r="BL41" s="0">
         <v>0</v>
@@ -15053,7 +15052,7 @@
         <v>0</v>
       </c>
       <c r="K42" s="0">
-        <v>1.8814139110604316</v>
+        <v>1.8814139110604315</v>
       </c>
       <c r="L42" s="0">
         <v>0.31965903036760757</v>
@@ -15113,7 +15112,7 @@
         <v>0.28551034975017819</v>
       </c>
       <c r="AE42" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF42" s="0">
         <v>0</v>
@@ -15347,7 +15346,7 @@
         <v>12.67759562841529</v>
       </c>
       <c r="DE42" s="0">
-        <v>8.1681971967133809</v>
+        <v>8.1681971967133808</v>
       </c>
       <c r="DF42" s="0">
         <v>0</v>
@@ -15374,7 +15373,7 @@
         <v>0</v>
       </c>
       <c r="DN42" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO42" s="0">
         <v>0</v>
@@ -15694,7 +15693,7 @@
         <v>12.71577923656697</v>
       </c>
       <c r="CZ43" s="0">
-        <v>5.8727569331158192</v>
+        <v>5.8727569331158191</v>
       </c>
       <c r="DA43" s="0">
         <v>0</v>
@@ -15747,7 +15746,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>0.47095761381475621</v>
+        <v>0.4709576138147562</v>
       </c>
       <c r="B44" s="0">
         <v>11.41495233316607</v>
@@ -15813,7 +15812,7 @@
         <v>2.1599264705882333</v>
       </c>
       <c r="W44" s="0">
-        <v>9.1794871794871718</v>
+        <v>9.1794871794871717</v>
       </c>
       <c r="X44" s="0">
         <v>2.6719727117680474</v>
@@ -16005,7 +16004,7 @@
         <v>0.039750894395123859</v>
       </c>
       <c r="CI44" s="0">
-        <v>6.1231281198003274</v>
+        <v>6.1231281198003273</v>
       </c>
       <c r="CJ44" s="0">
         <v>0</v>
@@ -16017,7 +16016,7 @@
         <v>0.17051913603637728</v>
       </c>
       <c r="CM44" s="0">
-        <v>8.4404695360536533</v>
+        <v>8.4404695360536532</v>
       </c>
       <c r="CN44" s="0">
         <v>3.3740129217516124</v>
@@ -16089,10 +16088,10 @@
         <v>2.6422764227642253</v>
       </c>
       <c r="DK44" s="0">
-        <v>2.9126213592232984</v>
+        <v>2.9126213592232983</v>
       </c>
       <c r="DL44" s="0">
-        <v>8.6161879895561278</v>
+        <v>8.6161879895561277</v>
       </c>
       <c r="DM44" s="0">
         <v>0</v>
@@ -16169,7 +16168,7 @@
         <v>8.9121081745543869</v>
       </c>
       <c r="U45" s="0">
-        <v>6.9157836029001612</v>
+        <v>6.9157836029001611</v>
       </c>
       <c r="V45" s="0">
         <v>6.7095588235294059</v>
@@ -16238,7 +16237,7 @@
         <v>1.8025751072961356</v>
       </c>
       <c r="AR45" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS45" s="0">
         <v>13.888888888888877</v>
@@ -16289,7 +16288,7 @@
         <v>4.5515394912985228</v>
       </c>
       <c r="BI45" s="0">
-        <v>6.3259817105970893</v>
+        <v>6.3259817105970892</v>
       </c>
       <c r="BJ45" s="0">
         <v>8.3692647871752275</v>
@@ -16370,7 +16369,7 @@
         <v>11.148086522462552</v>
       </c>
       <c r="CJ45" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK45" s="0">
         <v>1.0983397190293731</v>
@@ -16537,7 +16536,7 @@
         <v>11.488970588235283</v>
       </c>
       <c r="W46" s="0">
-        <v>1.3333333333333322</v>
+        <v>1.3333333333333321</v>
       </c>
       <c r="X46" s="0">
         <v>12.22285389425809</v>
@@ -16576,7 +16575,7 @@
         <v>15.688659166920022</v>
       </c>
       <c r="AJ46" s="0">
-        <v>8.7925696594427159</v>
+        <v>8.7925696594427158</v>
       </c>
       <c r="AK46" s="0">
         <v>5.3264987742366783</v>
@@ -16612,7 +16611,7 @@
         <v>8.2900593471810016</v>
       </c>
       <c r="AV46" s="0">
-        <v>2.8616141292197606</v>
+        <v>2.8616141292197605</v>
       </c>
       <c r="AW46" s="0">
         <v>8.3423035522066673</v>
@@ -16678,7 +16677,7 @@
         <v>11.234745154343134</v>
       </c>
       <c r="BR46" s="0">
-        <v>0.84766287236618954</v>
+        <v>0.84766287236618953</v>
       </c>
       <c r="BS46" s="0">
         <v>16.806009935780914</v>
@@ -16839,7 +16838,7 @@
         <v>5.5193176116407683</v>
       </c>
       <c r="C47" s="0">
-        <v>8.6610693769333143</v>
+        <v>8.6610693769333142</v>
       </c>
       <c r="D47" s="0">
         <v>4.4094746332268056</v>
@@ -16944,7 +16943,7 @@
         <v>1.8720748829953286</v>
       </c>
       <c r="AL47" s="0">
-        <v>7.0419810408203079</v>
+        <v>7.0419810408203078</v>
       </c>
       <c r="AM47" s="0">
         <v>13.901760889712762</v>
@@ -17133,7 +17132,7 @@
         <v>0</v>
       </c>
       <c r="CW47" s="0">
-        <v>7.4990899162723324</v>
+        <v>7.4990899162723323</v>
       </c>
       <c r="CX47" s="0">
         <v>13.13518696069038</v>
@@ -17157,7 +17156,7 @@
         <v>0.38251366120218755</v>
       </c>
       <c r="DE47" s="0">
-        <v>0.86998550024166677</v>
+        <v>0.86998550024166676</v>
       </c>
       <c r="DF47" s="0">
         <v>1.6359918200409076</v>
@@ -17225,7 +17224,7 @@
         <v>13.619796662190666</v>
       </c>
       <c r="K48" s="0">
-        <v>1.8814139110604316</v>
+        <v>1.8814139110604315</v>
       </c>
       <c r="L48" s="0">
         <v>5.1145444858817211</v>
@@ -17483,7 +17482,7 @@
         <v>1.5180568871844027</v>
       </c>
       <c r="CS48" s="0">
-        <v>9.6417514374170637</v>
+        <v>9.6417514374170636</v>
       </c>
       <c r="CT48" s="0">
         <v>10.192230676812166</v>
@@ -17501,13 +17500,13 @@
         <v>16.347075743048883</v>
       </c>
       <c r="CY48" s="0">
-        <v>0.24313153415998035</v>
+        <v>0.24313153415998034</v>
       </c>
       <c r="CZ48" s="0">
         <v>2.1440223724073624</v>
       </c>
       <c r="DA48" s="0">
-        <v>2.0893371757925055</v>
+        <v>2.0893371757925054</v>
       </c>
       <c r="DB48" s="0">
         <v>0.15673981191222555</v>
@@ -17519,7 +17518,7 @@
         <v>0.054644808743169349</v>
       </c>
       <c r="DE48" s="0">
-        <v>0.19333011116481375</v>
+        <v>0.19333011116481374</v>
       </c>
       <c r="DF48" s="0">
         <v>4.6012269938650263</v>
@@ -17584,7 +17583,7 @@
         <v>3.9867109634551459</v>
       </c>
       <c r="J49" s="0">
-        <v>16.420487243429872</v>
+        <v>16.420487243429871</v>
       </c>
       <c r="K49" s="0">
         <v>0.057012542759407023</v>
@@ -17680,7 +17679,7 @@
         <v>0</v>
       </c>
       <c r="AP49" s="0">
-        <v>9.8896247240618021</v>
+        <v>9.889624724061802</v>
       </c>
       <c r="AQ49" s="0">
         <v>11.931330472102992</v>
@@ -17707,7 +17706,7 @@
         <v>0.060771801883925801</v>
       </c>
       <c r="AY49" s="0">
-        <v>3.2355915065722925</v>
+        <v>3.2355915065722924</v>
       </c>
       <c r="AZ49" s="0">
         <v>0.57428677287884344</v>
@@ -17731,7 +17730,7 @@
         <v>0.45814244064972892</v>
       </c>
       <c r="BG49" s="0">
-        <v>3.3086876155267993</v>
+        <v>3.3086876155267992</v>
       </c>
       <c r="BH49" s="0">
         <v>9.6552878179384116</v>
@@ -17767,7 +17766,7 @@
         <v>0</v>
       </c>
       <c r="BS49" s="0">
-        <v>2.532412456076576</v>
+        <v>2.5324124560765759</v>
       </c>
       <c r="BT49" s="0">
         <v>0</v>
@@ -17806,7 +17805,7 @@
         <v>19.809523809523792</v>
       </c>
       <c r="CF49" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG49" s="0">
         <v>0</v>
@@ -17863,7 +17862,7 @@
         <v>14.141898370086277</v>
       </c>
       <c r="CY49" s="0">
-        <v>0.048626306831996064</v>
+        <v>0.048626306831996063</v>
       </c>
       <c r="CZ49" s="0">
         <v>0.51270100209741276</v>
@@ -17914,7 +17913,7 @@
         <v>6.0679611650485388</v>
       </c>
       <c r="DP49" s="0">
-        <v>7.3943661971830919</v>
+        <v>7.3943661971830918</v>
       </c>
     </row>
     <row r="50">
@@ -17958,7 +17957,7 @@
         <v>0</v>
       </c>
       <c r="N50" s="0">
-        <v>1.3084112149532699</v>
+        <v>1.3084112149532698</v>
       </c>
       <c r="O50" s="0">
         <v>15.819655922483673</v>
@@ -17988,7 +17987,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="0">
-        <v>1.4781125639567923</v>
+        <v>1.4781125639567922</v>
       </c>
       <c r="Y50" s="0">
         <v>0.23584905660377337</v>
@@ -18168,7 +18167,7 @@
         <v>15.809523809523796</v>
       </c>
       <c r="CF50" s="0">
-        <v>2.2452504317789273</v>
+        <v>2.2452504317789272</v>
       </c>
       <c r="CG50" s="0">
         <v>0</v>
@@ -18207,7 +18206,7 @@
         <v>0.015979546180888447</v>
       </c>
       <c r="CS50" s="0">
-        <v>1.6143299425033158</v>
+        <v>1.6143299425033157</v>
       </c>
       <c r="CT50" s="0">
         <v>1.7020424509411278</v>
@@ -18237,7 +18236,7 @@
         <v>2.5078369905956088</v>
       </c>
       <c r="DC50" s="0">
-        <v>0.20206555904804655</v>
+        <v>0.20206555904804654</v>
       </c>
       <c r="DD50" s="0">
         <v>0</v>
@@ -18326,7 +18325,7 @@
         <v>10.38164919912991</v>
       </c>
       <c r="P51" s="0">
-        <v>1.672069612694078</v>
+        <v>1.6720696126940779</v>
       </c>
       <c r="Q51" s="0">
         <v>7.7160493827160419</v>
@@ -18398,7 +18397,7 @@
         <v>0.27803521779425372</v>
       </c>
       <c r="AN51" s="0">
-        <v>4.4328552803129036</v>
+        <v>4.4328552803129035</v>
       </c>
       <c r="AO51" s="0">
         <v>0</v>
@@ -18461,7 +18460,7 @@
         <v>1.2382864792503336</v>
       </c>
       <c r="BI51" s="0">
-        <v>0.64550833781602957</v>
+        <v>0.64550833781602956</v>
       </c>
       <c r="BJ51" s="0">
         <v>0.18794914317302361</v>
@@ -18730,7 +18729,7 @@
         <v>0.92198581560283599</v>
       </c>
       <c r="AD52" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE52" s="0">
         <v>0.40983606557377017</v>
@@ -18907,10 +18906,10 @@
         <v>12.270714737507896</v>
       </c>
       <c r="CK52" s="0">
-        <v>1.1749680715197946</v>
+        <v>1.1749680715197945</v>
       </c>
       <c r="CL52" s="0">
-        <v>1.6009852216748755</v>
+        <v>1.6009852216748754</v>
       </c>
       <c r="CM52" s="0">
         <v>0</v>
@@ -19095,10 +19094,10 @@
         <v>0</v>
       </c>
       <c r="AE53" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF53" s="0">
-        <v>1.6842105263157881</v>
+        <v>1.684210526315788</v>
       </c>
       <c r="AG53" s="0">
         <v>1.7202354006337692</v>
@@ -19284,7 +19283,7 @@
         <v>0</v>
       </c>
       <c r="CP53" s="0">
-        <v>0.38373905744093984</v>
+        <v>0.38373905744093983</v>
       </c>
       <c r="CQ53" s="0">
         <v>0.53641092327698259</v>
@@ -20011,7 +20010,7 @@
         <v>0.02398369109005874</v>
       </c>
       <c r="CQ55" s="0">
-        <v>0.032509752925877739</v>
+        <v>0.032509752925877738</v>
       </c>
       <c r="CR55" s="0">
         <v>0</v>
@@ -20220,7 +20219,7 @@
         <v>0</v>
       </c>
       <c r="AR56" s="0">
-        <v>0.037383177570093421</v>
+        <v>0.03738317757009342</v>
       </c>
       <c r="AS56" s="0">
         <v>0</v>
@@ -21399,7 +21398,7 @@
         <v>0</v>
       </c>
       <c r="BW59" s="0">
-        <v>2.105263157894735</v>
+        <v>2.1052631578947349</v>
       </c>
       <c r="BX59" s="0">
         <v>0</v>
@@ -22123,7 +22122,7 @@
         <v>0</v>
       </c>
       <c r="BW61" s="0">
-        <v>0.043859649122806981</v>
+        <v>0.04385964912280698</v>
       </c>
       <c r="BX61" s="0">
         <v>0</v>
@@ -25342,7 +25341,7 @@
         <v>0</v>
       </c>
       <c r="BJ70" s="0">
-        <v>0.022111663902708662</v>
+        <v>0.022111663902708661</v>
       </c>
       <c r="BK70" s="0">
         <v>0</v>
@@ -25423,7 +25422,7 @@
         <v>0.25300442757748237</v>
       </c>
       <c r="CK70" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL70" s="0">
         <v>0</v>
@@ -25895,7 +25894,7 @@
         <v>0.081960495041389983</v>
       </c>
       <c r="E72" s="0">
-        <v>0.27100271002710003</v>
+        <v>0.27100271002710002</v>
       </c>
       <c r="F72" s="0">
         <v>0.034432297495050328</v>
@@ -26084,7 +26083,7 @@
         <v>0</v>
       </c>
       <c r="BP72" s="0">
-        <v>0.022045855379188691</v>
+        <v>0.02204585537918869</v>
       </c>
       <c r="BQ72" s="0">
         <v>0.32304379038047354</v>
@@ -26344,7 +26343,7 @@
         <v>0</v>
       </c>
       <c r="AH73" s="0">
-        <v>1.236917221693624</v>
+        <v>1.2369172216936239</v>
       </c>
       <c r="AI73" s="0">
         <v>0</v>
@@ -26389,7 +26388,7 @@
         <v>0.067069081153588131</v>
       </c>
       <c r="AW73" s="0">
-        <v>0.18837459634015053</v>
+        <v>0.18837459634015052</v>
       </c>
       <c r="AX73" s="0">
         <v>0</v>
@@ -26643,7 +26642,7 @@
         <v>1.2253596164091625</v>
       </c>
       <c r="M74" s="0">
-        <v>0.49896049896049855</v>
+        <v>0.49896049896049854</v>
       </c>
       <c r="N74" s="0">
         <v>0.031152647975077854</v>
@@ -26706,7 +26705,7 @@
         <v>0</v>
       </c>
       <c r="AH74" s="0">
-        <v>3.7583254043767807</v>
+        <v>3.7583254043767806</v>
       </c>
       <c r="AI74" s="0">
         <v>0</v>
@@ -26730,7 +26729,7 @@
         <v>0</v>
       </c>
       <c r="AP74" s="0">
-        <v>8.9624724061810071</v>
+        <v>8.962472406181007</v>
       </c>
       <c r="AQ74" s="0">
         <v>5.2789699570815403</v>
@@ -26895,7 +26894,7 @@
         <v>2.0773410035154987</v>
       </c>
       <c r="CS74" s="0">
-        <v>3.0738611233967244</v>
+        <v>3.0738611233967243</v>
       </c>
       <c r="CT74" s="0">
         <v>2.2026431718061654</v>
@@ -27056,7 +27055,7 @@
         <v>10.425531914893607</v>
       </c>
       <c r="AD75" s="0">
-        <v>0.071377587437544549</v>
+        <v>0.071377587437544548</v>
       </c>
       <c r="AE75" s="0">
         <v>0</v>
@@ -27188,13 +27187,13 @@
         <v>0</v>
       </c>
       <c r="BV75" s="0">
-        <v>1.3759213759213747</v>
+        <v>1.3759213759213746</v>
       </c>
       <c r="BW75" s="0">
         <v>0</v>
       </c>
       <c r="BX75" s="0">
-        <v>7.7408498106857318</v>
+        <v>7.7408498106857317</v>
       </c>
       <c r="BY75" s="0">
         <v>10.827759197324404</v>
@@ -27472,7 +27471,7 @@
         <v>7.9376854599406466</v>
       </c>
       <c r="AV76" s="0">
-        <v>4.4712720769058763</v>
+        <v>4.4712720769058762</v>
       </c>
       <c r="AW76" s="0">
         <v>7.5888051668460648</v>
@@ -27792,7 +27791,7 @@
         <v>1.2449071978270698</v>
       </c>
       <c r="AH77" s="0">
-        <v>12.535680304471923</v>
+        <v>12.535680304471922</v>
       </c>
       <c r="AI77" s="0">
         <v>0</v>
@@ -27885,7 +27884,7 @@
         <v>0</v>
       </c>
       <c r="BM77" s="0">
-        <v>0.15644011819920029</v>
+        <v>0.15644011819920028</v>
       </c>
       <c r="BN77" s="0">
         <v>0.031046258925799413</v>
@@ -27936,7 +27935,7 @@
         <v>0</v>
       </c>
       <c r="CD77" s="0">
-        <v>0.88461538461538381</v>
+        <v>0.8846153846153838</v>
       </c>
       <c r="CE77" s="0">
         <v>0</v>
@@ -28067,7 +28066,7 @@
         <v>10.228669781165468</v>
       </c>
       <c r="E78" s="0">
-        <v>7.2142790393421104</v>
+        <v>7.2142790393421103</v>
       </c>
       <c r="F78" s="0">
         <v>9.7012998192304298</v>
@@ -28510,7 +28509,7 @@
         <v>0</v>
       </c>
       <c r="AF79" s="0">
-        <v>6.5263157894736788</v>
+        <v>6.5263157894736787</v>
       </c>
       <c r="AG79" s="0">
         <v>6.631960162969663</v>
@@ -28678,7 +28677,7 @@
         <v>1.6971713810316125</v>
       </c>
       <c r="CJ79" s="0">
-        <v>0.031625553447185297</v>
+        <v>0.031625553447185296</v>
       </c>
       <c r="CK79" s="0">
         <v>1.0046828437633026</v>
@@ -28738,7 +28737,7 @@
         <v>0.022451728783116277</v>
       </c>
       <c r="DD79" s="0">
-        <v>0.2185792349726774</v>
+        <v>0.21857923497267739</v>
       </c>
       <c r="DE79" s="0">
         <v>8.0231996133397701</v>
@@ -28866,7 +28865,7 @@
         <v>0.070921985815602773</v>
       </c>
       <c r="AD80" s="0">
-        <v>9.0649536045681583</v>
+        <v>9.0649536045681582</v>
       </c>
       <c r="AE80" s="0">
         <v>0</v>
@@ -28965,7 +28964,7 @@
         <v>0.43117744610281883</v>
       </c>
       <c r="BK80" s="0">
-        <v>6.0993200082423194</v>
+        <v>6.0993200082423193</v>
       </c>
       <c r="BL80" s="0">
         <v>0</v>
@@ -29046,7 +29045,7 @@
         <v>0.19582801191996577</v>
       </c>
       <c r="CL80" s="0">
-        <v>1.6009852216748755</v>
+        <v>1.6009852216748754</v>
       </c>
       <c r="CM80" s="0">
         <v>8.9435438792621493</v>
@@ -29124,7 +29123,7 @@
         <v>0</v>
       </c>
       <c r="DL80" s="0">
-        <v>8.6161879895561278</v>
+        <v>8.6161879895561277</v>
       </c>
       <c r="DM80" s="0">
         <v>5.3418803418803371</v>
@@ -29156,7 +29155,7 @@
         <v>0.084104289318755174</v>
       </c>
       <c r="F81" s="0">
-        <v>0.46483601618317944</v>
+        <v>0.46483601618317943</v>
       </c>
       <c r="G81" s="0">
         <v>1.3621794871794859</v>
@@ -29261,7 +29260,7 @@
         <v>0.13037809647979129</v>
       </c>
       <c r="AO81" s="0">
-        <v>10.06741573033707</v>
+        <v>10.067415730337069</v>
       </c>
       <c r="AP81" s="0">
         <v>0.0883002207505518</v>
@@ -29372,7 +29371,7 @@
         <v>0</v>
       </c>
       <c r="BZ81" s="0">
-        <v>2.6461295418641369</v>
+        <v>2.6461295418641368</v>
       </c>
       <c r="CA81" s="0">
         <v>0.60150375939849576</v>
@@ -29405,7 +29404,7 @@
         <v>0</v>
       </c>
       <c r="CK81" s="0">
-        <v>0.017028522775649199</v>
+        <v>0.017028522775649198</v>
       </c>
       <c r="CL81" s="0">
         <v>0.36945812807881739</v>
@@ -29420,7 +29419,7 @@
         <v>13.409151018249128</v>
       </c>
       <c r="CP81" s="0">
-        <v>7.7227485309989144</v>
+        <v>7.7227485309989143</v>
       </c>
       <c r="CQ81" s="0">
         <v>0</v>
@@ -29492,7 +29491,7 @@
         <v>4.9145299145299104</v>
       </c>
       <c r="DN81" s="0">
-        <v>0.58593749999999945</v>
+        <v>0.58593749999999944</v>
       </c>
       <c r="DO81" s="0">
         <v>0</v>
@@ -29719,7 +29718,7 @@
         <v>4.3245993385907333</v>
       </c>
       <c r="BU82" s="0">
-        <v>1.0258004351880739</v>
+        <v>1.0258004351880738</v>
       </c>
       <c r="BV82" s="0">
         <v>0.58968058968059567</v>
@@ -29746,7 +29745,7 @@
         <v>9.6737907761530799</v>
       </c>
       <c r="CD82" s="0">
-        <v>6.7692307692308385</v>
+        <v>6.7692307692308384</v>
       </c>
       <c r="CE82" s="0">
         <v>0</v>
@@ -29848,7 +29847,7 @@
         <v>0</v>
       </c>
       <c r="DL82" s="0">
-        <v>9.7911227154048</v>
+        <v>9.7911227154047999</v>
       </c>
       <c r="DM82" s="0">
         <v>8.5470085470086339</v>
@@ -29958,7 +29957,7 @@
         <v>0</v>
       </c>
       <c r="AF83" s="0">
-        <v>1.6842105263157881</v>
+        <v>1.684210526315788</v>
       </c>
       <c r="AG83" s="0">
         <v>1.5617926663648696</v>
@@ -30072,7 +30071,7 @@
         <v>0</v>
       </c>
       <c r="BR83" s="0">
-        <v>0.84766287236618954</v>
+        <v>0.84766287236618953</v>
       </c>
       <c r="BS83" s="0">
         <v>1.2359142130134486</v>
@@ -30114,7 +30113,7 @@
         <v>0</v>
       </c>
       <c r="CF83" s="0">
-        <v>0.34542314335060415</v>
+        <v>0.34542314335060414</v>
       </c>
       <c r="CG83" s="0">
         <v>12.657330260592081</v>
@@ -30254,7 +30253,7 @@
         <v>0.033222591362126221</v>
       </c>
       <c r="J84" s="0">
-        <v>0.90159217341262155</v>
+        <v>0.90159217341262154</v>
       </c>
       <c r="K84" s="0">
         <v>0</v>
@@ -30766,7 +30765,7 @@
         <v>9.2975970425138552</v>
       </c>
       <c r="BH85" s="0">
-        <v>0.40160642570281086</v>
+        <v>0.40160642570281085</v>
       </c>
       <c r="BI85" s="0">
         <v>4.7875201721355518</v>
@@ -31227,7 +31226,7 @@
         <v>0</v>
       </c>
       <c r="CO86" s="0">
-        <v>0.066120074054482878</v>
+        <v>0.066120074054482877</v>
       </c>
       <c r="CP86" s="0">
         <v>0.01199184554502937</v>
@@ -32851,7 +32850,7 @@
         <v>0</v>
       </c>
       <c r="AE91" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF91" s="0">
         <v>0</v>
@@ -33213,7 +33212,7 @@
         <v>0</v>
       </c>
       <c r="AE92" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF92" s="0">
         <v>0</v>
@@ -33575,7 +33574,7 @@
         <v>0</v>
       </c>
       <c r="AE93" s="0">
-        <v>0.20491803278688509</v>
+        <v>0.20491803278688508</v>
       </c>
       <c r="AF93" s="0">
         <v>0</v>
